--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2025/Tháng 11/01. Báo giá bảo hành/BG_Maxconnect_111125.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2025/Tháng 11/01. Báo giá bảo hành/BG_Maxconnect_111125.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4.Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2025\Tháng 11\01. Báo giá bảo hành\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2025\Tháng 11\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D21E15-F194-4151-BE08-0C9AF21013E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BG" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$J$24</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -132,7 +133,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@*."/>
   </numFmts>
@@ -457,13 +458,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -550,22 +560,13 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -641,9 +642,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -681,9 +682,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -718,7 +719,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -753,7 +754,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -926,7 +927,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA43"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -949,81 +950,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22"/>
-      <c r="B1" s="23"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="32" t="s">
+      <c r="A1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="34"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="37"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="29" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="31"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="35" t="s">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="37"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="40"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="38" t="s">
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="47"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="50"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
@@ -1033,11 +1034,11 @@
       <c r="J6" s="12"/>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -1047,11 +1048,11 @@
       <c r="J7" s="12"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -1062,11 +1063,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
@@ -1110,75 +1111,75 @@
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53">
+      <c r="A11" s="21">
         <v>1</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="D11" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="49" t="s">
+      <c r="E11" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F11" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11" s="20">
         <v>900000</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11" s="20">
         <f>PRODUCT(H11:I11)</f>
         <v>900000</v>
       </c>
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="53"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="48" t="s">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="48" t="s">
+      <c r="G12" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12" s="20">
         <v>300000</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12" s="20">
         <f>PRODUCT(H12:I12)</f>
         <v>300000</v>
       </c>
       <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="7">
         <f>SUM(J11:J12)</f>
         <v>1200000</v>
@@ -1186,11 +1187,11 @@
       <c r="AA13" s="2"/>
     </row>
     <row r="14" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
@@ -1204,47 +1205,47 @@
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
       <c r="E17" s="14"/>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1315,20 +1316,20 @@
       <c r="AA22" s="2"/>
     </row>
     <row r="23" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
       <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1405,6 +1406,14 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="24">
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="F17:J17"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="F15:J15"/>
@@ -1421,17 +1430,9 @@
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="F17:J17"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" display="http://vnetgps.vn"/>
+    <hyperlink ref="D4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0" top="1.75" bottom="0" header="0" footer="0"/>
   <pageSetup scale="28" orientation="landscape" r:id="rId2"/>
